--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_348_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_348_R35.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0242</v>
+        <v>7.1934</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0416</v>
+        <v>4.942</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9826</v>
+        <v>2.2515</v>
       </c>
       <c r="G2" t="n">
         <v>4.6464</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7486</v>
+        <v>0.4206</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1177</v>
+        <v>0.7826</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6308</v>
+        <v>-0.362</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6559</v>
+        <v>4.1167</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3255</v>
+        <v>3.2822</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3304</v>
+        <v>0.8345</v>
       </c>
       <c r="G3" t="n">
         <v>2.8754</v>
@@ -688,13 +688,13 @@
         <v>3.4793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1595</v>
+        <v>0.6203</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0069</v>
+        <v>0.9636</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8474</v>
+        <v>-0.3433</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.3758</v>
+        <v>3.4279</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1015</v>
+        <v>2.6913</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2743</v>
+        <v>0.7366</v>
       </c>
       <c r="G4" t="n">
         <v>2.2277</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>0.058</v>
+        <v>0.11</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.507</v>
+        <v>0.0828</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5649</v>
+        <v>0.0272</v>
       </c>
       <c r="V4" t="n">
         <v>0.3943</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7806</v>
+        <v>1.6291</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7678</v>
+        <v>1.6498</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0129</v>
+        <v>-0.0207</v>
       </c>
       <c r="G5" t="n">
         <v>-0.695</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7798</v>
+        <v>0.6282</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8417</v>
+        <v>0.7237</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0619</v>
+        <v>-0.0955</v>
       </c>
       <c r="V5" t="n">
         <v>0.5361</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3122</v>
+        <v>1.1771</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1923</v>
+        <v>1.9564</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8801</v>
+        <v>-0.7792</v>
       </c>
       <c r="G6" t="n">
         <v>1.3118</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2324</v>
+        <v>0.0973</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7943</v>
+        <v>0.5583</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5619</v>
+        <v>-0.461</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2666</v>
+        <v>0.3749</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7273</v>
+        <v>-1.6527</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9939</v>
+        <v>2.0275</v>
       </c>
       <c r="G7" t="n">
         <v>1.5536</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2464</v>
+        <v>0.3547</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8927</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5715</v>
+        <v>-0.5379</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5919</v>
+        <v>0.2913</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6251</v>
+        <v>-0.8427</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0332</v>
+        <v>1.1341</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2569</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6365</v>
+        <v>0.2467</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4244</v>
+        <v>0.358</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2122</v>
+        <v>-0.1114</v>
       </c>
       <c r="V8" t="n">
         <v>0.1418</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2103</v>
+        <v>-0.9243</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9772</v>
+        <v>-0.8592</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2332</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0394</v>
@@ -1156,13 +1156,13 @@
         <v>1.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1709</v>
+        <v>0.1151</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3462</v>
+        <v>0.4641</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6151</v>
+        <v>-3.5277</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9969</v>
+        <v>-1.4484</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3818</v>
+        <v>-2.0793</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7497</v>
+        <v>-3.8719</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7059</v>
+        <v>-3.3902</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0439</v>
+        <v>-0.4817</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0171</v>
+        <v>-1.6492</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2379</v>
+        <v>-3.0109</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2208</v>
+        <v>1.3618</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.7326</v>
+        <v>-2.2227</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5321</v>
+        <v>-0.3792</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2647</v>
+        <v>-1.8435</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.7112</v>
+        <v>-0.232</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>4.1321</v>
+        <v>0.633</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7314</v>
+        <v>0.4327</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4007</v>
+        <v>0.2003</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.1444</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4947</v>
+        <v>-3.8816</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6843</v>
+        <v>-3.9274</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8104</v>
+        <v>0.0458</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8719</v>
+        <v>-2.7497</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.3902</v>
+        <v>-1.7059</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4817</v>
+        <v>-1.0439</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6492</v>
+        <v>-2.0171</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.0109</v>
+        <v>-2.2379</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3618</v>
+        <v>0.2208</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2227</v>
+        <v>-0.7326</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3792</v>
+        <v>0.5321</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8435</v>
+        <v>-1.2647</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8556</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.232</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>0.666</v>
+        <v>1.8655</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1968</v>
+        <v>1.8009</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4692</v>
+        <v>0.0646</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1444</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.503299999999999</v>
+        <v>9.876800000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.417899999999999</v>
+        <v>5.791300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.0854</v>
+        <v>4.085700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>3.002000000000002</v>
@@ -1378,7 +1378,7 @@
         <v>0.8182</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.3022</v>
+        <v>-5.302200000000001</v>
       </c>
       <c r="P12" t="n">
         <v>2.3196</v>
@@ -1390,10 +1390,10 @@
         <v>17.3965</v>
       </c>
       <c r="S12" t="n">
-        <v>4.718200000000001</v>
+        <v>5.0914</v>
       </c>
       <c r="T12" t="n">
-        <v>6.686199999999999</v>
+        <v>7.0594</v>
       </c>
       <c r="U12" t="n">
         <v>-1.968</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0383</v>
+        <v>4.8018</v>
       </c>
       <c r="E13" t="n">
         <v>3.9483</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0901</v>
+        <v>0.8536</v>
       </c>
       <c r="G13" t="n">
         <v>5.0442</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3822</v>
+        <v>0.3813</v>
       </c>
       <c r="T13" t="n">
         <v>0.1221</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5043</v>
+        <v>0.2592</v>
       </c>
       <c r="V13" t="n">
         <v>0.5361</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1108</v>
+        <v>2.9485</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1938</v>
+        <v>1.6041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.917</v>
+        <v>1.3444</v>
       </c>
       <c r="G14" t="n">
         <v>1.0988</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8522</v>
+        <v>0.6899</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8338</v>
+        <v>0.244</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0185</v>
+        <v>0.4459</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0963</v>
+        <v>1.645</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8943</v>
+        <v>2.2582</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2021</v>
+        <v>-0.6132</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1271</v>
+        <v>1.5277</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4382</v>
+        <v>1.6748</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3111</v>
+        <v>-0.1471</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2385</v>
+        <v>1.842</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8605</v>
+        <v>1.1427</v>
       </c>
       <c r="L15" t="n">
-        <v>0.378</v>
+        <v>0.6993</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1115</v>
+        <v>-0.3143</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4223</v>
+        <v>0.5321</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6891</v>
+        <v>-0.8464</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6651</v>
+        <v>0.5838</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2072</v>
+        <v>0.5939</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5421</v>
+        <v>-0.0101</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8226</v>
+        <v>1.5687</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1674</v>
+        <v>1.1865</v>
       </c>
       <c r="F16" t="n">
-        <v>0.99</v>
+        <v>0.3822</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.03</v>
+        <v>0.1271</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1741</v>
+        <v>0.4382</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2041</v>
+        <v>-0.3111</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9528</v>
+        <v>1.2385</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5749</v>
+        <v>0.8605</v>
       </c>
       <c r="L16" t="n">
         <v>0.378</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9829</v>
+        <v>-1.1115</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4008</v>
+        <v>-0.4223</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5821</v>
+        <v>-0.6891</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.539</v>
+        <v>0.1375</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0395</v>
+        <v>0.4995</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5786</v>
+        <v>-0.362</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3196</v>
+        <v>0.7611</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7864</v>
+        <v>-0.2853</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4668</v>
+        <v>1.0465</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5277</v>
+        <v>-0.03</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6748</v>
+        <v>0.1741</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1471</v>
+        <v>-0.2041</v>
       </c>
       <c r="J17" t="n">
-        <v>1.842</v>
+        <v>0.9528</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1427</v>
+        <v>0.5749</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6993</v>
+        <v>0.378</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3143</v>
+        <v>-0.9829</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5321</v>
+        <v>-0.4008</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8464</v>
+        <v>-0.5821</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7415</v>
+        <v>-0.6005</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1221</v>
+        <v>-0.0784</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8637</v>
+        <v>-0.5221</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4511</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2072</v>
+        <v>0.0287</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2439</v>
+        <v>-0.0194</v>
       </c>
       <c r="G18" t="n">
         <v>0.5816</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1228</v>
+        <v>-0.6625</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8988</v>
+        <v>-0.6743</v>
       </c>
       <c r="V18" t="n">
         <v>-0.1418</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.269</v>
+        <v>-2.0453</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9306</v>
+        <v>-2.8084</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3385</v>
+        <v>0.7631</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0047</v>
+        <v>-0.9669</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6002</v>
+        <v>3.276</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5955</v>
+        <v>-4.2429</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8266</v>
+        <v>0.4409</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7897999999999999</v>
+        <v>2.1041</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-1.6633</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.822</v>
+        <v>-1.4077</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1896</v>
+        <v>1.1719</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6323</v>
+        <v>-2.5796</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0876</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-3.9432</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0444</v>
+        <v>0.5632</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5623</v>
+        <v>0.016</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6067</v>
+        <v>0.5472</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2713</v>
+        <v>-2.0696</v>
       </c>
       <c r="E20" t="n">
         <v>-0.8925</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3788</v>
+        <v>-1.1772</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6456</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7855</v>
+        <v>-0.5838</v>
       </c>
       <c r="T20" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V20" t="n">
         <v>-0.5361</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5571</v>
+        <v>-2.5893</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9263</v>
+        <v>-1.2844</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3693</v>
+        <v>-1.3049</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9669</v>
+        <v>0.0047</v>
       </c>
       <c r="H21" t="n">
-        <v>3.276</v>
+        <v>0.6002</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.2429</v>
+        <v>-0.5955</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4409</v>
+        <v>0.8266</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1041</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.6633</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4077</v>
+        <v>-0.822</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1719</v>
+        <v>-0.1896</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.5796</v>
+        <v>-0.6323</v>
       </c>
       <c r="P21" t="n">
+        <v>-2.0876</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-2.3195</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-3.9432</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0514</v>
+        <v>-0.3646</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1019</v>
+        <v>0.2084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1533</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="V21" t="n">
-        <v>0.6778999999999999</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1339</v>
+        <v>-2.8644</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7052</v>
+        <v>-1.4693</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4286</v>
+        <v>-1.395</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4629</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5988</v>
+        <v>-0.3293</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1971</v>
+        <v>-2.8883</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.0694</v>
+        <v>-1.9515</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1277</v>
+        <v>-0.9368</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8357</v>
@@ -2248,13 +2248,13 @@
         <v>0.232</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4336</v>
+        <v>-0.1248</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4876</v>
+        <v>0.6056</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9212</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.0117</v>
+        <v>-4.8493</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0097</v>
+        <v>-4.4199</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.002</v>
+        <v>-0.4294</v>
       </c>
       <c r="G24" t="n">
         <v>-5.4449</v>
@@ -2326,13 +2326,13 @@
         <v>2.3195</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.639</v>
+        <v>-0.4766</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4832</v>
+        <v>0.1065</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1558</v>
+        <v>-0.5832000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>1.0722</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.503600000000002</v>
+        <v>-5.5718</v>
       </c>
       <c r="E25" t="n">
         <v>-4.0855</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.4178</v>
+        <v>-1.4861</v>
       </c>
       <c r="G25" t="n">
         <v>-3.0019</v>
       </c>
       <c r="H25" t="n">
-        <v>2.251099999999999</v>
+        <v>2.2511</v>
       </c>
       <c r="I25" t="n">
         <v>-5.253200000000001</v>
@@ -2404,16 +2404,16 @@
         <v>15.0771</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.718100000000001</v>
+        <v>-0.7863999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>1.968</v>
+        <v>1.9679</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.6862</v>
+        <v>-2.7543</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5360999999999998</v>
+        <v>0.5360999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>6.8586</v>
